--- a/01_Thermal/B_results/single_annular_bemt_analysis.xlsx
+++ b/01_Thermal/B_results/single_annular_bemt_analysis.xlsx
@@ -526,40 +526,40 @@
         <v>195</v>
       </c>
       <c r="E2" t="n">
-        <v>21.23034888276955</v>
+        <v>15.74136675760155</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1790337042390744</v>
+        <v>0.200199477459167</v>
       </c>
       <c r="G2" t="n">
-        <v>384.7538168782789</v>
+        <v>481.1042808632454</v>
       </c>
       <c r="H2" t="n">
         <v>12003.65050354092</v>
       </c>
       <c r="I2" t="n">
-        <v>0.08321777323475649</v>
+        <v>0.03272727100230934</v>
       </c>
       <c r="J2" t="n">
-        <v>0.3267531353996254</v>
+        <v>0.3261941025205431</v>
       </c>
       <c r="K2" t="n">
-        <v>0.1592142315968851</v>
+        <v>0.1640863154085699</v>
       </c>
       <c r="L2" t="n">
-        <v>6.086974999998554</v>
+        <v>6.086974999999974</v>
       </c>
       <c r="M2" t="n">
-        <v>0.4500784376668589</v>
+        <v>0.5213973820164834</v>
       </c>
       <c r="N2" t="n">
-        <v>0.09415691330475341</v>
+        <v>0.01833918594600815</v>
       </c>
       <c r="O2" t="n">
-        <v>0.314785875998468</v>
+        <v>0.3124349295186446</v>
       </c>
       <c r="P2" t="n">
-        <v>0.4633983334006478</v>
+        <v>0.3065603555780633</v>
       </c>
     </row>
     <row r="3">
@@ -578,40 +578,40 @@
         <v>195</v>
       </c>
       <c r="E3" t="n">
-        <v>5.668852558738038</v>
+        <v>5.715846048479664</v>
       </c>
       <c r="F3" t="n">
-        <v>0.07996431579217228</v>
+        <v>0.08042360027047932</v>
       </c>
       <c r="G3" t="n">
-        <v>62.68447974670278</v>
+        <v>63.40661905839916</v>
       </c>
       <c r="H3" t="n">
         <v>9803.193489796937</v>
       </c>
       <c r="I3" t="n">
-        <v>0.008384341400370881</v>
+        <v>0.009777166758466663</v>
       </c>
       <c r="J3" t="n">
-        <v>0.323667251378589</v>
+        <v>0.3249706626873308</v>
       </c>
       <c r="K3" t="n">
-        <v>0.2339611978038382</v>
+        <v>0.2277459752437846</v>
       </c>
       <c r="L3" t="n">
-        <v>5.088974421483914</v>
+        <v>5.127708995387021</v>
       </c>
       <c r="M3" t="n">
-        <v>0.4146021544798534</v>
+        <v>0.4230373828174782</v>
       </c>
       <c r="N3" t="n">
-        <v>0.1362677716981878</v>
+        <v>0.1190264249918382</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.1828054695406122</v>
+        <v>-0.1631656107868411</v>
       </c>
       <c r="P3" t="n">
-        <v>1.025702511217095</v>
+        <v>1.031015945819364</v>
       </c>
     </row>
     <row r="4">
@@ -630,40 +630,40 @@
         <v>195</v>
       </c>
       <c r="E4" t="n">
-        <v>16.59049271261133</v>
+        <v>15.94634930060045</v>
       </c>
       <c r="F4" t="n">
-        <v>0.2585428255325475</v>
+        <v>0.2355882788682354</v>
       </c>
       <c r="G4" t="n">
-        <v>607.6802882051696</v>
+        <v>504.5654700417957</v>
       </c>
       <c r="H4" t="n">
         <v>9090.968804657296</v>
       </c>
       <c r="I4" t="n">
-        <v>0.02138040549404825</v>
+        <v>0.01699823061018332</v>
       </c>
       <c r="J4" t="n">
-        <v>0.5264766940001046</v>
+        <v>0.5385440176638251</v>
       </c>
       <c r="K4" t="n">
-        <v>0.1843331687081108</v>
+        <v>0.176078734875025</v>
       </c>
       <c r="L4" t="n">
-        <v>3.961601196597131</v>
+        <v>3.888210673990142</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.9992704576236295</v>
+        <v>-0.9359672813149343</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.03070415440489609</v>
+        <v>-0.07154178292117275</v>
       </c>
       <c r="O4" t="n">
-        <v>0.3693800548231223</v>
+        <v>-0.1392030687295198</v>
       </c>
       <c r="P4" t="n">
-        <v>0.2249655880633936</v>
+        <v>0.2188911534119586</v>
       </c>
     </row>
     <row r="5">
@@ -682,40 +682,40 @@
         <v>195</v>
       </c>
       <c r="E5" t="n">
-        <v>11.19106949504114</v>
+        <v>11.04409625860778</v>
       </c>
       <c r="F5" t="n">
-        <v>0.08539191443856033</v>
+        <v>0.08617252786071368</v>
       </c>
       <c r="G5" t="n">
-        <v>522.388879854037</v>
+        <v>531.9834101861111</v>
       </c>
       <c r="H5" t="n">
         <v>71640.79933933764</v>
       </c>
       <c r="I5" t="n">
-        <v>0.007256628191884316</v>
+        <v>0.01290537763945257</v>
       </c>
       <c r="J5" t="n">
-        <v>0.3315298022030728</v>
+        <v>0.3868246307004896</v>
       </c>
       <c r="K5" t="n">
-        <v>0.4157485777967798</v>
+        <v>0.3482175860986065</v>
       </c>
       <c r="L5" t="n">
-        <v>2.881802560377761</v>
+        <v>2.949561235470975</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.4048600846470232</v>
+        <v>-0.3317360942396267</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.1820131239736304</v>
+        <v>-0.2952988191539074</v>
       </c>
       <c r="O5" t="n">
-        <v>0.1941091433986639</v>
+        <v>0.1991232011505641</v>
       </c>
       <c r="P5" t="n">
-        <v>0.7502505853439153</v>
+        <v>0.5974062768108837</v>
       </c>
     </row>
     <row r="6">
@@ -734,40 +734,40 @@
         <v>195</v>
       </c>
       <c r="E6" t="n">
-        <v>10.17897780581054</v>
+        <v>9.343089484779309</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1155068077496673</v>
+        <v>0.1214153129805146</v>
       </c>
       <c r="G6" t="n">
-        <v>214.091794911384</v>
+        <v>236.5548124440824</v>
       </c>
       <c r="H6" t="n">
         <v>16046.66774128612</v>
       </c>
       <c r="I6" t="n">
-        <v>0.006413601258043545</v>
+        <v>0.007518124415006624</v>
       </c>
       <c r="J6" t="n">
-        <v>0.4023144864005901</v>
+        <v>0.3856165154331307</v>
       </c>
       <c r="K6" t="n">
-        <v>0.3931140170889311</v>
+        <v>0.3945288114201675</v>
       </c>
       <c r="L6" t="n">
-        <v>2.153894214091423</v>
+        <v>2.303926135717681</v>
       </c>
       <c r="M6" t="n">
-        <v>0.2534982534432125</v>
+        <v>-0.0004710425412296048</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.3782667062170901</v>
+        <v>-0.1577504495608363</v>
       </c>
       <c r="O6" t="n">
-        <v>0.3723630141147607</v>
+        <v>0.176265709282811</v>
       </c>
       <c r="P6" t="n">
-        <v>0.6831018026581483</v>
+        <v>1.081440011169387</v>
       </c>
     </row>
     <row r="7">
@@ -786,40 +786,40 @@
         <v>195</v>
       </c>
       <c r="E7" t="n">
-        <v>10.22901498905244</v>
+        <v>9.768173673940444</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1762270663019447</v>
+        <v>0.172036073103058</v>
       </c>
       <c r="G7" t="n">
-        <v>167.828274860209</v>
+        <v>159.9406840169159</v>
       </c>
       <c r="H7" t="n">
         <v>5404.056829595333</v>
       </c>
       <c r="I7" t="n">
-        <v>0.007281559057604298</v>
+        <v>0.005262525188478381</v>
       </c>
       <c r="J7" t="n">
-        <v>0.4008533778421772</v>
+        <v>0.3970853870922503</v>
       </c>
       <c r="K7" t="n">
-        <v>0.421242793993894</v>
+        <v>0.413953405098165</v>
       </c>
       <c r="L7" t="n">
-        <v>2.426871659489694</v>
+        <v>2.443875547753798</v>
       </c>
       <c r="M7" t="n">
-        <v>0.2513600927753623</v>
+        <v>0.2399232928015362</v>
       </c>
       <c r="N7" t="n">
-        <v>0.385322480702235</v>
+        <v>0.3869036695220629</v>
       </c>
       <c r="O7" t="n">
-        <v>0.2380991796724366</v>
+        <v>0.2548940119901126</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.02238401476897605</v>
+        <v>-0.04016494703747209</v>
       </c>
     </row>
     <row r="8">
@@ -838,40 +838,40 @@
         <v>195</v>
       </c>
       <c r="E8" t="n">
-        <v>8.332479046504359</v>
+        <v>8.496424967406242</v>
       </c>
       <c r="F8" t="n">
-        <v>0.07003125003597803</v>
+        <v>0.06795771281551649</v>
       </c>
       <c r="G8" t="n">
-        <v>95.75746601578157</v>
+        <v>90.17089821339411</v>
       </c>
       <c r="H8" t="n">
         <v>19524.90314262347</v>
       </c>
       <c r="I8" t="n">
-        <v>0.002918597112675285</v>
+        <v>0.005511646149815067</v>
       </c>
       <c r="J8" t="n">
-        <v>0.3882706649423203</v>
+        <v>0.379460764348199</v>
       </c>
       <c r="K8" t="n">
-        <v>0.5312832446391645</v>
+        <v>0.5293412824551286</v>
       </c>
       <c r="L8" t="n">
-        <v>1.999286954720624</v>
+        <v>1.961897172743173</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.01991117448202355</v>
+        <v>0.0452937126901163</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.03731867093779978</v>
+        <v>0.03307503318409424</v>
       </c>
       <c r="O8" t="n">
-        <v>0.1343341731495304</v>
+        <v>0.1596425294303053</v>
       </c>
       <c r="P8" t="n">
-        <v>0.1603946198391386</v>
+        <v>0.1207200654339963</v>
       </c>
     </row>
     <row r="9">
@@ -888,13 +888,13 @@
         <v>1365</v>
       </c>
       <c r="E9" t="n">
-        <v>83.42123549052739</v>
+        <v>76.05534649141543</v>
       </c>
       <c r="F9" t="n">
-        <v>0.1196679808588437</v>
+        <v>0.1200325452304683</v>
       </c>
       <c r="G9" t="n">
-        <v>2055.185000471562</v>
+        <v>2067.726174823944</v>
       </c>
       <c r="H9" t="n">
         <v>143514.2398508377</v>
